--- a/指导书工作台/作业指导书版头.xlsx
+++ b/指导书工作台/作业指导书版头.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="23040" windowHeight="9060" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1 (清单)" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="1" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="2取消" sheetId="3" state="hidden" r:id="rId3"/>
-    <sheet name="新格式" sheetId="4" state="hidden" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1 (清单)" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2取消" sheetId="3" state="hidden" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="新格式" sheetId="4" state="hidden" r:id="rId4"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'Sheet1 (清单)'!$1:$3</definedName>
@@ -5480,7 +5480,7 @@
       <c r="L7" s="403" t="n"/>
       <c r="M7" s="1" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
     </row>
@@ -5857,7 +5857,7 @@
       <c r="L30" s="99" t="n"/>
       <c r="O30" s="1" t="inlineStr">
         <is>
-          <t>                                                                          </t>
+          <t xml:space="preserve">                                                                          </t>
         </is>
       </c>
     </row>
